--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -46,6 +46,7 @@
     <sheet name="2026-07-08" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="2026-07-15" sheetId="38" state="visible" r:id="rId38"/>
     <sheet name="2026-07-22" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="2026-07-29" sheetId="40" state="visible" r:id="rId40"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46488,6 +46489,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ワンパンマン</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア ~クソゲーハンター、神ゲーに挑まんとす~</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BUNGO-unreal-</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ダイヤモンドの功罪</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TSUYOSHI 誰も勝てない、アイツには</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>本好きの下剋上~司書になるためには手段を選んでいられません~第三部 「領地に本を広げよう!10」</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MIX</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 2 Page</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DEAR BOYS ACT4</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ジャンケットバンク</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>終末のワルキューレ禁伝 神々の黙示録</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>冒険家になろう!~スキルボードでダンジョン攻略~(コミック)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>異世界でスローライフを(願望)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>無自覚最硬タンクのおかしな牧場</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>骸骨騎士様、只今異世界へお出掛け中 寄り道編</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>花野井くんと恋の病</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>龍と苺</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>100万の命の上に俺は立っている</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>解雇された暗黒兵士のスローなセカンドライフ</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>星降る王国のニナ</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>すだちの魔王城</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>天幕のジャードゥーガル</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>余りモノ異世界人の自由生活 勇者じゃないので勝手にやらせてもらいます7</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>実力主義に拾われた鑑定士 ~奴隷扱いだった母国を捨てて、敵国の英雄はじめました~5</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>片田舎のおっさん、剣聖になる~ただの田舎の剣術師範だったのに、大成した弟子たちが俺を放ってくれない件~</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>終末のワルキューレ奇譚 ジャック・ザ・リッパーの事件簿</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>前田慶次 かぶき旅</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ひとりぼっちの異世界攻略</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>転生して田舎でスローライフをおくりたい</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>弱虫ペダル</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>春の嵐とモンスター</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>転生貴族の万能開拓~スキルを使っていたら最強領地になりました~</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>無駄飯食らい認定されたので愛想をつかし、帝国に移って出世する ~王国の偉い人にはそれが分からんのです~</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>獣王と薬草</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>出会って5秒でバトル</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>アオアシ ブラザーフット</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>青のミブロー新選組編ー</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>野良猫と狼</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>アオのハコ</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>角栄に花束を</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ミリモス・サーガ-末弟王子の転生戦記</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>君のことが大大大大大好きな100人の彼女</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>だれでも抱けるキミが好き</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>劣等人の魔剣使い スキルボードを駆使して最強に至る</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>高校時代に傲慢だった女王様との同棲生活は意外と居心地が悪くない</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Sランク冒険者である俺の娘たちは重度のファザコンでした</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ヘルモード ~やり込み好きのゲーマーは廃設定の異世界で無双する~はじまりの召喚士14</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>シャドーハウス</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ダーウィン事変</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>のあ先輩はともだち。</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>老後に備えて異世界で8万枚の金貨を貯めます</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>領民0人スタートの辺境領主様 ~青のディアスと蒼角の乙女~15</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>桃源暗鬼</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SPY×FAMILY</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>29歳独身中堅冒険者の日常</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>悪役令嬢の取り巻きやめようと思います 1(アリアンローズコミックス)</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>鬼の花嫁</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>夢幻のノエル</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>あなたたちに捨てられた私は、ようやく幸せになれそうです</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>職業王妃ですので王の溺愛はご遠慮願います</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>蜂蜜令嬢の契約結婚 雇われ妻に甘い恋は不要です!?</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>鬼の花嫁</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>手札が多めのビクトリア</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>寝取り魔法使いの冒険</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>絢爛たるグランドセーヌ</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>異世界でテイムした最強の使い魔は、幼馴染の美少女でした</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>リィンカーネーションの花弁</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>勇者パーティーにかわいい子がいたので、告白してみた。(コミック)</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ケイ×ヤク -あぶない相棒-</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>JJM 女子柔道部物語 社会人編</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>味方が弱すぎて補助魔法に徹していた宮廷魔法師、追放されて最強を目指す</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ガベージブレイブ 異世界に召喚され捨てられた勇者の復讐物語</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>罪と罰のスピカ</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>サンダー3</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>フェルマーの料理</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>王様ランキング</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>宝石の娘と異能の王子 単行本版</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ここは俺に任せて先に行けと言ってから10年がたったら伝説になっていた。</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>高嶺のハナさん</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>欠けた月のメルセデス~吸血鬼の貴族に転生したけど捨てられそうなのでダンジョンを制覇する~@COMIC</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>刃牙らへん</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>あの島の海音荘</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ 通常版</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>チェンソーマン</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -47,6 +47,7 @@
     <sheet name="2026-07-15" sheetId="38" state="visible" r:id="rId38"/>
     <sheet name="2026-07-22" sheetId="39" state="visible" r:id="rId39"/>
     <sheet name="2026-07-29" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="2026-08-05" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -47825,6 +47826,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>宇宙兄弟</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>薬屋のひとりごと</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GIANT KILLING</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>メダリスト</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>望郷太郎</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>平和の国の島崎へ</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ワンパンマン</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア ~クソゲーハンター、神ゲーに挑まんとす~</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BUNGO-unreal-</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ダンジョンに出会いを求めるのは間違っているだろうかⅡ</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ギルドを追放された回復術士、実は魔力無限だったので規格外の回復魔法で伝説となる1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>人形姫は恋を占う</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>魔性、聖者に堕つ。</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>執事殿の愛猫</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>出禁のモグラ</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>「壇蜜」</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>転移先は薬師が少ない世界でした7</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ダンジョンに出会いを求めるのは間違っているだろうか 外伝 ソード・オラトリア</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>無能と蔑まれたが、実は伝説のでした~500年前の仲間&amp;魔王の娘と一緒に今度こそ世界を救います~1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>怠惰な獣と檻の中</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>七王国のバラ</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>魔女と貴血の騎士</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>妖王の花嫁</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>片田舎のおっさん、剣聖になる~ただの田舎の剣術師範だったのに、大成した弟子たちが俺を放ってくれない件~</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>追放されるたびにスキルを手に入れた俺が、100の異世界で2周目無双</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>初めて恋をした日に読む話</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>天上の箱庭遊戯</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>火の姫と水の皇。</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>玉座と小夜啼鳥</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>GARIYA-世界に君しかいない-</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>天と献上姫</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>飼主は悪魔</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>神サマ学園@あるめりあ</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>黒と黒</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>レア・ジュエル</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>王のいばら</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HIGH&amp;HIGH</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>地雷なんですか?地原さん</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>花野井くんと恋の病</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MIX</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Re:blue</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>執事殿の愛猫</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>恋情sparkle</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>恋する宇宙</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>G・DEFEND</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ダイヤモンドの功罪</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>調教師は魔物に囲まれて生きていきます。~勇者パーティーに置いていかれたけど、伝説の魔物と出会い最強になってた~</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>春の嵐とモンスター</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>火の姫と水の皇。</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>玉座と小夜啼鳥</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>玉座と小夜啼鳥</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>玉座と小夜啼鳥</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>玉座と小夜啼鳥</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>玉座と小夜啼鳥</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>玉座と小夜啼鳥</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>玉座と小夜啼鳥</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>玉座と小夜啼鳥</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>七王国のバラ</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>魔女と貴血の騎士</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>天と献上姫</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>飼主は悪魔</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>黒と黒</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>レア・ジュエル</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>レア・ジュエル</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>レア・ジュエル</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MOON・TRICK</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>王のいばら</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>王のいばら</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>王のいばら</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>王のいばら</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>王のいばら</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ベスポジ!</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>S級ヒーロー!</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>人生は結果オーライ!</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>御来訪学園へようこそ!</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>KING</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>アスタリスク</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>海老原さん家は今日も大変!</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>田舎のホームセンター男の自由な異世界生活</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>宇宙兄弟</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ドクターチルドレン~小児外科医~</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>転生悪役幼女は最恐パパの愛娘になりました</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>骸骨騎士様、只今異世界へお出掛け中 寄り道編</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>TSUYOSHI 誰も勝てない、アイツには</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>青のミブロー新選組編ー</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>地球が終わるらしいので、いまからキミを監禁します。</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>未来にんにゃニニニちゃん 1話</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>GARIYA-世界に君しかいない-</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -48,6 +48,7 @@
     <sheet name="2026-07-22" sheetId="39" state="visible" r:id="rId39"/>
     <sheet name="2026-07-29" sheetId="40" state="visible" r:id="rId40"/>
     <sheet name="2026-08-05" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="2026-08-12" sheetId="42" state="visible" r:id="rId42"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49162,6 +49163,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>薬屋のひとりごと</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ブラッククローバー</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>宇宙兄弟</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>あかね噺</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ワンパンマン</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>らーめん再遊記</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>転生悪役幼女は最恐パパの愛娘になりました</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>元婚約者から逃げるため吸血伯爵に恋人のフリをお願いしたら、なぜか溺愛モードになりました</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>メダリスト</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>婚約破棄は本望です!聖女の力が開花したので私は自由に暮らします~本物の聖女は義姉ではなく私でした~</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>召喚ですか!? ハッカドール</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>逃げ上手の若君</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>創傷イモータルフラワー</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>異世界転移したら愛犬が最強になりました~シルバーフェンリルと俺が異世界暮らしを始めたら~ THE COMIC</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>レベル1から始まる召喚無双 THE COMIC</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ROPPEN-六篇-</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>闇金ウシジマくん外伝 肉蝮伝説</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>離縁予定の捨てられ令嬢ですが、なぜか次期公爵様の溺愛が始まりました</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>くのいち女子高生 音無さん</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ちゅぱからぶ</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LIFE GAME</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>夜ノ子-the doom liberators-</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>GIANT KILLING</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>楠木さんは高校デビューに失敗している:</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>真の聖女である私は追放されました。だからこの国はもう終わりです</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>忘却バッテリー</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>黄昏流星群</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>悪祓士のキヨシくん</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>だって、私はフリーダム! 魔工士フェイ、古代文明に挑みます 第1話</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>賢者の弟子を名乗る賢者外伝~ミラと素敵な召喚精霊たち~</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AR/MS!!(エーアール・マルチプルサヴァイヴ)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>冥婚の契</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>サムライハーフ</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>夜鬼</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>みいちゃんと山田さん</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>みいちゃんと山田さん</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>みいちゃんと山田さん</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>みいちゃんと山田さん</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>みいちゃんと山田さん</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>壁役など不要と追放されたS級冒険者、≪奴隷解放≫スキルを駆使して史上最強の国造り:</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア ~クソゲーハンター、神ゲーに挑まんとす~</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>憂国のモリアーティ</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ウィッチウォッチ</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Blood Redemption 前編</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>あきらめないでよ、さとりちゃん</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>僕のかわいい娘は双子の賢者 ~特技がデバフの底辺黒魔導士、育てた双子の娘がSランクの大賢者になってしまう~</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>僕のかわいい娘は双子の賢者 ~特技がデバフの底辺黒魔導士、育てた双子の娘がSランクの大賢者になってしまう~</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>追放されたドラゴン好き令嬢は、北方辺境伯の愛に気づかない</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Berry’sFantasyならば、悪女になりましょう~亡き者にした令嬢からやり返される気分はいかがですか?~</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>意地悪姉と呼ばれた令嬢、実はとても優れた魔法使いでした。@COMIC 第1話</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>後宮見鬼の嫁入り@COMIC 第1話</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>S級ギルドを追放されたけど、実は俺だけドラゴンの言葉がわかるので、気付いたときには竜騎士の頂点を極めてました。</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>結界師の一輪華</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>追放されるたびにスキルを手に入れた俺が、100の異世界で2周目無双</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>江戸前の旬</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>平和の国の島崎へ</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>出禁のモグラ</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>戦場の聖女 ~妹の代わりに公爵騎士に嫁ぐことになりましたが、今は幸せです~</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>望郷太郎</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>永年雇用は可能でしょうか</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>永年雇用は可能でしょうか</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>永年雇用は可能でしょうか</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>永年雇用は可能でしょうか</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>永年雇用は可能でしょうか</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>シリアルキラー異世界に降り立つ</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり 通常版</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり 通常版</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり 通常版</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ヘルモード ~やり込み好きのゲーマーは廃設定の異世界で無双する~はじまりの召喚士14</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>バツイチがモテるなんて聞いてません</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>追放された元雑用係、規格外の技術で「最高の修繕師」と呼ばれるようになりました~SSSランクパーティーや王族からの依頼が止まりません~</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>初めて恋をした日に読む話</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>MIX</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>チェンソーマン</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 2 Page</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>宮中葬礼譚 若返りの老宮女は不老の役人と魂を送る</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>山奥育ちの俺のゆるり異世界生活~もふもふと最強たちに可愛がられて、二度目の人生満喫中~</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>山奥育ちの俺のゆるり異世界生活~もふもふと最強たちに可愛がられて、二度目の人生満喫中~</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>人外剣士は力に魅せられ裏迷宮を攻略す~化け物扱いされた元冒険者は、自分だけが知る迷宮で人目を気にせず無双する~</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>転生した先は地獄でした――三百年続く辺境伯家の防衛戦線</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>鑑定士ロイのこじらせ愛は今日も華麗に空回る</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>鑑定士ロイのこじらせ愛は今日も華麗に空回る</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>鑑定士ロイのこじらせ愛は今日も華麗に空回る</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>幼馴染みで悪魔な騎士は、私のことが大嫌い ~New Round~</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>幼馴染みで悪魔な騎士は、私のことが大嫌い ~New Round~</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>幼馴染みで悪魔な騎士は、私のことが大嫌い ~New Round~</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -49,6 +49,7 @@
     <sheet name="2026-07-29" sheetId="40" state="visible" r:id="rId40"/>
     <sheet name="2026-08-05" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="2026-08-12" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="2026-08-19" sheetId="43" state="visible" r:id="rId43"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -50499,6 +50500,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ブラッククローバー</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐&amp;『ざまぁ!』します!</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>アンダーニンジャ</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>転生賢者の異世界ライフ~第二の職業を得て、世界最強になりました~</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>薬屋のひとりごと</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>宇宙兄弟</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件 異聞 ~魔国暮らしのトリニティ~</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ゲーム中盤で死ぬ悪役貴族に転生したので、外れスキルを駆使して最強を目指してみた</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>パリピ孔明</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>あかね噺</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>妹は知っている</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>片田舎のおっさん、剣聖になる外伝 はじまりの魔法剣士</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>信長協奏曲</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>弱虫ペダル SPARE BIKE</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>逃げ上手の若君</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>忘却バッテリー</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>グラぱらっ!</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件 クレイマンREVENGE</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>独身貴族は異世界を謳歌する ~結婚しない男の優雅なおひとりさまライフ~</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>怪物事変</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>異世界魔王と召喚少女の奴隷魔術</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>裏バイト:逃亡禁止</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ワンパンマン</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>彼岸島 48日後…</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>月刊少女野崎くん</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>中華一番!極</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>憂国のモリアーティ</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ババンババンバンバンパイア</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>税金で買った本</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>平成敗残兵すみれちゃん</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>追放された転生王子、『自動製作』スキルで領地を爆速で開拓し最強の村を作ってしまう~最強クラフトスキルで始める、楽々領地開拓スローライフ~</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>世界最強の魔女、始めました ~私だけ『攻略サイト』を見れる世界で自由に生きます~</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Aランクパーティを離脱した俺は、元教え子たちと迷宮深部を目指す。</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>灰宮先輩は怖くてかわいい</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>はじめてのセフレ</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ウィッチウォッチ</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ゴッドオブキラーズ</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>伍と碁</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ハナバス 苔石花江のバスケ論</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>クマ撃ちの女</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>この世界は不完全すぎる</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>異世界領地改革~土魔法で始める公共事業~</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BREAK BACK</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>俺だけ最強超越者~全世界のチート師匠に認められた~</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ゴッドオブキラーズ</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>創剣の大英雄~神に愛されたガラクタ~</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>闇堕ち暴君の執着が止まりません</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>メダリスト</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>黄昏町プリズナーズ</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>あくまでクジャクの話です。</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>戦鬼と呼ばれた男、王家に暗殺されたら娘を拾い、一緒にスローライフをはじめる innocent days7</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>土かぶりのエレナ姫</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>極と蕾~極道と恋を知らない人妻と~</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>友達んちの姉ちゃんが怖くていい人</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>追放令嬢、クラフトしながらキャンピングカーで異世界を旅します</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>俺だけ最強超越者~全世界のチート師匠に認められた~</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>帰ってきた天才剣聖~魔力ゼロの落ちこぼれなのに実は最強~</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>不死たる異端者と災いの竜姫</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>片田舎のおっさん、剣聖になる~ただの田舎の剣術師範だったのに、大成した弟子たちが俺を放ってくれない件~</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>GIANT KILLING</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ブーツレグ</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>幼稚園WARS</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>今夜もシリアルキラーと待ち合わせ</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>アオバノバスケ</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ヤニねこ</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア ~クソゲーハンター、神ゲーに挑まんとす~</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>レベル1から始まる召喚無双 THE COMIC</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ジュミドロ</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>追放されたチート付与魔術師は気ままなセカンドライフを謳歌する。 ~俺は武器だけじゃなく、あらゆるものに『強化ポイント』を付与できるし、俺の意思でいつでも効果を解除できるけど、残った人たち大丈夫?~</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ダイヤモンドの功罪</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>最強タンクの迷宮攻略 ~体力9999のレアスキル持ちタンク、勇者パーティーを追放される~</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BUNGO-unreal-</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>8歳から始める魔法学</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>闇金ウシジマくん外伝 肉蝮伝説</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>山と食欲と私</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>さむわんへるつ</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ブラッククローバー</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>召喚ですか!? ハッカドール</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>アフタヌーンティーはいかがですか? 私と先輩の、不純で一途なふたり暮らし</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>人外カルテ</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>特許やぶりの女王 弁理士・大鳳未来</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>田舎で恋は難しい!?</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>貴族の三男、でくの坊から最強魔術士へ。パラメーターを調節して、すべての魔術を魔改造!</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -50,6 +50,7 @@
     <sheet name="2026-08-05" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="2026-08-12" sheetId="42" state="visible" r:id="rId42"/>
     <sheet name="2026-08-19" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="2026-08-26" sheetId="44" state="visible" r:id="rId44"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -51836,6 +51837,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 2 Page</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>メイドインアビス</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ブラッククローバー</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>転生賢者の異世界ライフ~第二の職業を得て、世界最強になりました~</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>彼女、お借りします</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐&amp;『ざまぁ!』します!</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>神様のバレー</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>宇宙兄弟</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>月刊少女野崎くん</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ワンパンマン</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>THE BAND</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>裏バイト:逃亡禁止</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>隣のステラ</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>灰仭巫覡</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>黒岩メダカに私の可愛いが通じない</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MAJOR 2nd(メジャーセカンド)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件 クレイマンREVENGE</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>薬屋のひとりごと</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>むせるくらいの愛をあげる</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>俺だけ最強超越者~全世界のチート師匠に認められた~</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>私たちはどうかしている 妻恋い</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>学園騎士のレベルアップ!レベル1000超えの転生者、落ちこぼれクラスに入学。そして、(コミック)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>信長協奏曲</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>あおざくら 防衛大学校物語</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>おしえて執事くん</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>チェンソーマン</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>おっさんはうぜぇぇぇんだよ!ってギルドから追放したくせに、後から復帰要請を出されても遅い。最高の仲間と出会った俺はこっちで最強を目指す! コミック版</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>メダリスト</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>器用貧乏、城を建てる~開拓学園の劣等生なのに、上級職のスキルと魔法がすべて使えます~@COMIC</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>アンダーニンジャ</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Aランクパーティを離脱した俺は、元教え子たちと迷宮深部を目指す。</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>あくまでクジャクの話です。</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>グラぱらっ!</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>スライム倒して300年、知らないうちにレベルMAXになってました</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>憂国のモリアーティ</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>龍と苺</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>とことんクズな渡良瀬なのに</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 2 Page</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>俺だけ最強超越者~全世界のチート師匠に認められた~</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>雷雷雷</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>みいちゃんと山田さん</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件 異聞 ~魔国暮らしのトリニティ~</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>はじめてのセフレ</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>宝石箱に愛をつめよう</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>逃げ上手の若君</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>俺だけ最強超越者~全世界のチート師匠に認められた~</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>アルカナディア Cross Connect</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>僕らの恋はもどかしい</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>妻よ、僕の恋人になってくれませんか? 第1話</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>俺だけ最強超越者~全世界のチート師匠に認められた~</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>9番目のムサシ ゴースト アンド グレイ</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>役立たず冒険者で英雄に! 課金するほどチート機能が手に入るんですが!?</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>負けヒロインが多すぎる!@comic</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>忘却バッテリー</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ハナバス 苔石花江のバスケ論</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ダーウィン事変</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>平和の国の島崎へ</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ソアラと魔物の家</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>片田舎のおっさん、剣聖になる外伝 はじまりの魔法剣士</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>竜馬がゆく</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>異世界領地改革~土魔法で始める公共事業~</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>忌み子と呼ばれた召喚士@COMIC</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TSUYOSHI 誰も勝てない、アイツには</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ふたりバス</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>真夜中ハートチューン</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>青の祓魔師</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>パラショッパーズ</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>怪物事変</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>チェンソーマン</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -51,6 +51,7 @@
     <sheet name="2026-08-12" sheetId="42" state="visible" r:id="rId42"/>
     <sheet name="2026-08-19" sheetId="43" state="visible" r:id="rId43"/>
     <sheet name="2026-08-26" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="2026-09-02" sheetId="45" state="visible" r:id="rId45"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53173,6 +53174,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ブラック・ラグーン</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ドラフトキング</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ありふれた職業で世界最強</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>バトルスタディーズ</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>バトルスタディーズ</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>メイドインアビス</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ゾン100~ゾンビになるまでにしたい100のこと~</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>望まぬ不死の冒険者</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>彼女、お借りします</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>THE NEW GATE18</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MAJOR 2nd(メジャーセカンド)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>雑用付与術師が自分の最強に気付くまで(コミック)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ひとりぼっちの異世界攻略</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>薬屋のひとりごと</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>史上最強の魔法剣士、Fランク冒険者に転生する ~剣聖と魔帝、2つの前世を持った男の英雄譚~</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>大自然の魔法師アシュト、廃れた領地でスローライフ8</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ディグイット</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>転生賢者の異世界ライフ~第二の職業を得て、世界最強になりました~</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>もう興味がないと離婚された令嬢の意外と楽しい新生活</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 2 Page</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>宇宙兄弟</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>THE BAND</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>魔女大戦 32人の異才の魔女は殺し合う</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>信長協奏曲</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ブラッククローバー</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>波よ聞いてくれ</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>一勝千金</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>黒岩メダカに私の可愛いが通じない</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>聖なる乙女と秘めごとを</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>間違い召喚! 追い出されたけど上位互換スキルでらくらく生活6</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>テンカイチ 日本最強武芸者決定戦</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>追放者食堂へようこそ!11 ~最強パーティーを追放された料理人は、冒険者食堂を開きます!~</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ワンパンマン</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>GIANT KILLING</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>俺だけ不遇スキルの異世界召喚叛逆記~最弱スキルが全てを飲み込むまで~</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア ~クソゲーハンター、神ゲーに挑まんとす~</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐&amp;『ざまぁ!』します!</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>二階堂地獄ゴルフ</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>だんドーン</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>月刊少女野崎くん</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>龍と苺</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>あおざくら 防衛大学校物語</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>敗けサキュ×リリアの美味なる夜</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>恋知らずの神様に捧ぐ</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ギルド追放された雑用係の下剋上~超万能な生活スキルで世界最強~</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>一緒に暮らしていいですか?</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>忘却バッテリー</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>異世界じゃスローライフはままならない ~聖獣の主人は島育ち~7</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>国を追われた竜師さん、拾われた隣国でうっかり無双してしまう。~弱小国家が大陸最強の竜の楽園になるまで~</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>上野くんは開発済み</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>フシノカミ 11 ~辺境から始める文明再生記~</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>史上最強の弟子ケンイチ2 ~達人編~</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>しあわせ食堂の異世界ご飯</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>憂国のモリアーティ</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>たまのこしいれ ―アシガールEDO―</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>敗けサキュ×リリアの美味なる夜</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>敗けサキュ×リリアの美味なる夜</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>異世界で手に入れた生産スキルは最強だったようです。 ~創造&amp;器用のWチートで無双する~</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>圧倒的ガチャ運で異世界を成り上がる!</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>社畜テイマー、可愛いスライムのおかげで無自覚なまま無双する~うっかり国内トップの配信に映り込んで最強がバレました~</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>アンダーニンジャ</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>8月31日のロングサマー</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>引退したおっさん賢者だが愛弟子が追放されてきたので傷心旅行に連れて行く ~スローライフな旅のつもりが、なぜか世界最強の師弟になっていた~</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>神様のバレー</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BUNGO-unreal-</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SHIORI EXPERIENCE ジミなわたしとヘンなおじさん</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>みずぽろ</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>俺の前世の知識で底辺職テイマーが上級職になってしまいそうな件</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>弱虫ペダル SPARE BIKE</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>弱虫ペダル</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>中華一番!極</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>むせるくらいの愛をあげる</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>パラショッパーズ</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>逃げ上手の若君</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ウィッチウォッチ</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>怪物事変</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>社長が私を抱く理由</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>花嫁の座を奪われた忌み姫は楽しい亡命生活はじめます!1</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -52,6 +52,7 @@
     <sheet name="2026-08-19" sheetId="43" state="visible" r:id="rId43"/>
     <sheet name="2026-08-26" sheetId="44" state="visible" r:id="rId44"/>
     <sheet name="2026-09-02" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="2026-09-09" sheetId="46" state="visible" r:id="rId46"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54510,6 +54511,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>メイドインアビス</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>雑用付与術師が自分の最強に気付くまで(コミック)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>S級ギルドを離脱した刀鍛冶の自由な辺境スローライフ~ブラックギルドから解放されて気ままに鍛冶してたら、伝説の魔刀が生まれていました~</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>あかりは雪姫になりたい —根暗な引きこもりがVtuberになった理由—</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>マイホームアフロ田中</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S級ギルドを離脱した刀鍛冶の自由な辺境スローライフ~ブラックギルドから解放されて気ままに鍛冶してたら、伝説の魔刀が生まれていました~</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ドラフトキング</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>世界で一番『可愛い』雨宮さん、二番目は俺。 THE COMIC</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>冒険者パーティーを追放された回復士の少女を拾って育成したら、まさかの最強職業に転職!? おまけに彼女の様子が何やらおかしくて…:</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ありふれた職業で世界最強</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>彼女、お借りします</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>異世界ガイドマップ</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>だって、私はフリーダム! 魔工士フェイ、古代文明に挑みます 第2話</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>異世界転移したら愛犬が最強になりました ~シルバーフェンリルと俺が異世界暮らしを始めたら~ THE COMIC</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>霜月さんはモブが好き~人見知りな彼女は俺にだけデレ甘い~</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ダンジョンが現れて5年、15歳でダンジョンに挑むことにした。</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>悪役令嬢の兄に転生しました</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>バトルスタディーズ</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>バトルスタディーズ</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>薬屋のひとりごと</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>追放された転生貴族、外れスキルで内政無双~気ままに領地運営するはずが、スキル『ガチャ』のお陰で最強領地を作り上げてしまった~</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>虎王の花嫁さん</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ワンパンマン</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>保健室とふたり</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>異世界ガイドマップ</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>異世界ガイドマップ</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>うちのメイドがクラスの好きな子に似ている</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>バイト先のネットカフェが、なぜかクラスの美少女たちの溜まり場になった件。 第2話</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>最終兵器家族 第2話</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>僕の職業適性には人権がなかったらしい</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ブチ切れ令嬢は報復を誓いました。1~魔導書の力で祖国を叩き潰します~</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>契約婚した相手が鬼宰相でしたが、この度宰相室専任補佐官に任命された地味文官(変装中)は私です。</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SHIORI EXPERIENCE ジミなわたしとヘンなおじさん</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>転生賢者の異世界ライフ~第二の職業を得て、世界最強になりました~</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MAJOR 2nd(メジャーセカンド)</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>アクアプエラ-四季ノ森高校水泳部-</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>保健室とふたり</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>メゾンデスハイツ ~魔王の娘だけど弟子にしてください~</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>私はサキュバスじゃありません</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>うちのメイドがクラスの好きな子に似ている</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>うちのメイドがクラスの好きな子に似ている</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>婚約破棄ですか?はい喜んで。だって僕は姉の代わりですから! 第1話</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>転生したら剣でした Another Wish</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>超!!! 天才発明令嬢のパワフル領地改革1</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>才女のお世話1 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>新米オッサン冒険者、最強パーティに死ぬほど鍛えられて無敵になる。</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>日本へようこそエルフさん。</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>魔王の俺が奴隷エルフを嫁にしたんだが、どう愛でればいい?1</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>異世界料理道1</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>インフィニット・デンドログラム1</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ウォルテニア戦記1</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>宇宙兄弟</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>いびってこない義母と義姉:</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>転生無敗の異世界賢者~ゲームのジョブで楽しいセカンドライフ~</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>恋知らずの神様に捧ぐ</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>猫と竜</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>国を追われた竜師さん、拾われた隣国でうっかり無双してしまう。~弱小国家が大陸最強の竜の楽園になるまで~</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件 異聞 ~魔国暮らしのトリニティ~</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>THE NEW GATE18</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>貴族家三男の成り上がりライフ 生まれてすぐに人外認定された少年は異世界を満喫する4</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>昭和天皇物語</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>望まぬ不死の冒険者</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ブラック・ラグーン</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>オーイ! とんぼ</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ウィッチウォッチ</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ユメかウツツか</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>たまのこしいれ ―アシガールEDO―</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>保健室とふたり</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>メゾンデスハイツ ~魔王の娘だけど弟子にしてください~</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>メゾンデスハイツ ~魔王の娘だけど弟子にしてください~</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>私はサキュバスじゃありません</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>私はサキュバスじゃありません</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>アクアプエラ-四季ノ森高校水泳部-</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>アクアプエラ-四季ノ森高校水泳部-</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>バイト先のネットカフェが、なぜかクラスの美少女たちの溜まり場になった件。 第3話</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>婚約破棄ですか?はい喜んで。だって僕は姉の代わりですから! 第2話</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>聖属性ヒーラーは女騎士団の助っ人回復術師をやってます</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>センパイ、自宅警備員の雇用はいかがですか? THE COMIC</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>邪竜幼女~村娘に転生した最強ドラゴンは傍若無人に無双する~ 第1話</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ピークアウト</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>転生してあらゆるモノに好かれながら異世界で好きな事をして生きて行く</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>夜行堂奇譚</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -53,6 +53,7 @@
     <sheet name="2026-08-26" sheetId="44" state="visible" r:id="rId44"/>
     <sheet name="2026-09-02" sheetId="45" state="visible" r:id="rId45"/>
     <sheet name="2026-09-09" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="2026-09-16" sheetId="47" state="visible" r:id="rId47"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55847,6 +55848,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ダンダダン</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>カグラバチ</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>魔入りました!入間くん</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>女の園の星</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>異世界料理道1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ねずみの初恋</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>超!!! 天才発明令嬢のパワフル領地改革1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>勇者パーティーを追放されたビーストテイマー、最強種の猫耳少女と出会う</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>あなたのお城の小人さん ~御飯下さい、働きますっ~(コミック) 通常版</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>弱虫ペダル</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>新テニスの王子様</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>鵺の陰陽師</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>転生したら剣でした Another Wish</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>異世界転生で賢者になって冒険者生活 ~で異世界最強~</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>しのびごと</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>新米オッサン冒険者、最強パーティに死ぬほど鍛えられて無敵になる。</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ブチ切れ令嬢は報復を誓いました。1~魔導書の力で祖国を叩き潰します~</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>世界で一番『可愛い』雨宮さん、二番目は俺。 THE COMIC</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S級ギルドを離脱した刀鍛冶の自由な辺境スローライフ~ブラックギルドから解放されて気ままに鍛冶してたら、伝説の魔刀が生まれていました~</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>こちら葛飾区亀有公園前派出所</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ドラゴンクエスト ダイの大冒険 勇者アバンと獄炎の魔王</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>日本へようこそエルフさん。</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ひまてん!</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DARK SUN</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>才女のお世話1 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ゴールデンドロップ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>左ききのエレン</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ウォルテニア戦記1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>「姉のスペア」と呼ばれた身代わり人生は、今日でやめることにします~辺境で自由を満喫中なので、今さら真の聖女と言われても知りません!~1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>娘に断罪される悪役公爵に転生してました 悪役ムーブをやめたのになぜか娘が『氷の令嬢』化する件</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>メイドインアビス</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>俺だけ最強超越者~全世界のチート師匠に認められた~</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>モンスターがあふれる世界になったので、好きに生きたいと思います</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>二度転生した少年はSランク冒険者として平穏に過ごす ~前世が賢者で英雄だったボクは来世では地味に生きる~</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ワンパンマン</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>エクストラ・エキストラ</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>紅一献!~恋、ひとしずく~</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>俺だけ最強超越者~全世界のチート師匠に認められた~</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>年の差七の旦那様 ~不器用な辺境侯に溺愛されて~</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>悪名高い令嬢は敵国の王弟殿下に娶られる</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>泣き虫女中の初恋~次期当主様との優しい約束~</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>娘に断罪される悪役公爵に転生してました 悪役ムーブをやめたのになぜか娘が『氷の令嬢』化する件</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>娘に断罪される悪役公爵に転生してました 悪役ムーブをやめたのになぜか娘が『氷の令嬢』化する件</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>令嬢VTuberはメイドの夜食に蹂躙される~禁断ご飯で食レポ生配信~</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>雑用付与術師が自分の最強に気付くまで(コミック)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>暴力万歳</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ドローイング 最強漫画家はお絵描きスキルで異世界無双する!20</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>エリスの聖杯</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>左遷された最強賢者、教師になって無敵のクラスを作り上げる</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>オーイ! とんぼ</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>魔王の俺が奴隷エルフを嫁にしたんだが、どう愛でればいい?1</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>インフィニット・デンドログラム1</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>妻よ、僕の恋人になってくれませんか? 第1話</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ノアの渡航券</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>クズ騎士様の愛は激重につき!</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>エルマの騎士~堅物軍人は孤独な魔女の心を溶かしたい~</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ゼロ0~時空魔法で未来を超える~ 第1話</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>鬼姫はうちのなか</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>令嬢VTuberはメイドの夜食に蹂躙される~禁断ご飯で食レポ生配信~</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>令嬢VTuberはメイドの夜食に蹂躙される~禁断ご飯で食レポ生配信~</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>軍人婿さんと大根嫁さん</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>異世界で孤児院を開いたけど、なぜか誰一人巣立とうとしない件</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>バキ外伝 烈海王は異世界転生しても一向にかまわんッッ</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ゴールデンマン</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり 通常版</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>おかえり水平線</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>最強の魔導士。ひざに矢をうけてしまったので田舎の衛兵になる</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>マイホームアフロ田中</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MIX</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>それでも弟は恋したがる</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>MAJOR 2nd(メジャーセカンド)</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>チェンソーマン</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>黒猫の剣士~ブラックなパーティを辞めたらS級冒険者にスカウトされました。今さら「戻ってきて」と言われても「もう遅い」です~</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>黒猫の剣士~ブラックなパーティを辞めたらS級冒険者にスカウトされました。今さら「戻ってきて」と言われても「もう遅い」です~</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>黒猫の剣士~ブラックなパーティを辞めたらS級冒険者にスカウトされました。今さら「戻ってきて」と言われても「もう遅い」です~</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>霜月さんはモブが好き~人見知りな彼女は俺にだけデレ甘い~</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>売られた赤錆の花嫁は竜騎士様の最愛となる1</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>泉くんの考えた恋愛ゲームが無理すぎる</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ノアの渡航券</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ノアの渡航券</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>クズ騎士様の愛は激重につき!</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>クズ騎士様の愛は激重につき!</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ステルス令嬢の恋愛事情</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ステルス令嬢の恋愛事情</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ステルス令嬢の恋愛事情</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>戦利品令嬢シェリルは自分を殺す夫を籠絡したい</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>戦利品令嬢シェリルは自分を殺す夫を籠絡したい</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>戦利品令嬢シェリルは自分を殺す夫を籠絡したい</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>聖女の私が殺された!</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>義兄ヴァンパイアは毒の乙女を囲い込む第1話</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -54,6 +54,7 @@
     <sheet name="2026-09-02" sheetId="45" state="visible" r:id="rId45"/>
     <sheet name="2026-09-09" sheetId="46" state="visible" r:id="rId46"/>
     <sheet name="2026-09-16" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="2026-09-23" sheetId="48" state="visible" r:id="rId48"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -57184,6 +57185,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>薫る花は凛と咲く</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏 ~パーティ事情で付与術士をやっていた剣士、万能へと至る~</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>みいちゃんと山田さん</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>うるわしの宵の月</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>魔入りました!入間くん</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>弱虫ペダル</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>聖者無双</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ケンガンオメガ</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ダンダダン</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>女の園の星</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>辺境の薬師、都でSランク冒険者となる~英雄村の少年がチート薬で無自覚無双~</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>鬼の花嫁</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>実は俺、最強でした?</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>時々ボソッとロシア語でデレる隣のアーリャさん</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>不徳のギルド</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>失格紋の最強賢者 ~世界最強の賢者が更に強くなるために転生しました~</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ティアムーン帝国物語~断頭台から始まる、姫の転生逆転ストーリー~@COMIC</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>なのに、千輝くんが甘すぎる。</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>カグラバチ</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>勇者パーティーを追放されたビーストテイマー、最強種の猫耳少女と出会う</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>明日、結婚式なんですけど!?~婚約者に浮気されたので過去に戻って人生やりなおします~ 1(アリアンローズコミックス)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>殲滅魔導の最強賢者 無才の賢者、魔導を極め最強へ至る</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ちはやふる plus きみがため</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥~生まれ変わって今更やり直す2度目の学院生活~</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>脇役に転生したはずが、いつの間にか伝説の錬金術師になってた ~仲間たちが英雄でも俺は支援職なんだが~</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>火の神さまの掃除人ですが、いつの間にか花嫁として溺愛されています</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>やんごとなき一族</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>転生したら平民でした。~生活水準に耐えられないので貴族を目指します~(コミック)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ダンス・ダンス・ダンスール</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>勘違いの工房主 英雄パーティの元雑用係が、実は戦闘以外がSSSランクだったというよくある話10</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>マチネとソワレ</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>かわいくないかわいいあの子 第4話</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>バキ外伝 烈海王は異世界転生しても一向にかまわんッッ</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>江戸前の旬</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>貸した魔力はで強制徴収~用済みとパーティー追放された俺は、可愛いサポート妖精と一緒に取り立てた魔力を運用して最強を目指す。~</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>転生幼女はあきらめない</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>無能なナナ</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>今宵もお待ちしております</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ダウナー女神は推しが強い</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>勇者の元仲間夫婦は田舎でのんびり幸せに暮らす</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ジャンル「ホラー」レンタル不可</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Demons Roots 約束された敗北</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>黄金の経験値</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>女友達は頼めば意外とヤらせてくれる</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>最強で最速の無限レベルアップ ~スキルとでレベル上限の枷が外れた俺は無双する~</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>追放された底辺職「盗賊」はゲーム知識で無双する。一緒に召喚された先生も外れジョブだったけど効率的に成り上がります</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>念願の悪役令嬢の身体を手に入れたぞ!</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ハズレ属性土魔法のせいで辺境に追放されたので、ガンガン領地開拓します!5</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>薬屋のひとりごと</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>勇者パーティーを追放された俺だが、俺から巣立ってくれたようで嬉しい。……なので大聖女、お前に追って来られては困るのだが?(コミック)</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>暗殺後宮~暗殺女官・花鈴はゆったり生きたい~</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す ~公爵家の落ちこぼれ令嬢、嫁ぎ先で幸せを掴み取る~9</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>世界の果ては深愛</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ドラゴンクエスト ダイの大冒険 勇者アバンと獄炎の魔王</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>悪女ランキング</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>前世から君だけを愛すると誓うよ</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ワタシ悪役令嬢、いま無人島にいるの。……と思ったけどチート王子住んでた。1</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>メイドインアビス</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>異世界のんびり農家</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>怪獣自衛隊</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ねずみの初恋</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>タワーダンジョン</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>生まれ変わった剣聖、剣士が冷遇される魔術至上主義の学園で無双する</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>異世界転生で賢者になって冒険者生活 ~で異世界最強~</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>最強は田舎農家のおっさんでした~最高ランクのドラゴンを駆除した結果、実力が世界にバレました~</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>とある魔術の禁書目録</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>左ききのエレン</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>35歳恋愛処女、猫間くんに迫られてます1</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ときときチャンネル</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>闇堕ち暴君の執着が止まりません</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>死亡遊戯で飯を食う。</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>死亡遊戯で飯を食う。</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>最強の剣神、辺境の村娘に生まれ変わる。1</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>氷河系アイドルのマネージャーをしていますが、もう限界です。1</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>勇者学園の西園寺オスカー1</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>転生貴族の異世界冒険録~カインのやりすぎギルド日記~(ポルカコミックス)11</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>きみは四葉のクローバー</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>彼は友達</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>モンスターがあふれる世界になったので、好きに生きたいと思います</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>二度転生した少年はSランク冒険者として平穏に過ごす ~前世が賢者で英雄だったボクは来世では地味に生きる~</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>あなたのお城の小人さん ~御飯下さい、働きますっ~(コミック) 通常版</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>気絶勇者と暗殺姫</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>新テニスの王子様</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>MIX</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ワンパンマン</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ダウナー女神は推しが強い</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ダウナー女神は推しが強い</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>勇者の元仲間夫婦は田舎でのんびり幸せに暮らす</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>勇者の元仲間夫婦は田舎でのんびり幸せに暮らす</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>警視庁特犯課007</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>警視庁特犯課007</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -55,6 +55,7 @@
     <sheet name="2026-09-09" sheetId="46" state="visible" r:id="rId46"/>
     <sheet name="2026-09-16" sheetId="47" state="visible" r:id="rId47"/>
     <sheet name="2026-09-23" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="2026-09-30" sheetId="49" state="visible" r:id="rId49"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -58521,6 +58522,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BUNGO-unreal-</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ジョジョの奇妙な冒険 ザ・ジョジョランズ</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>超人X</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>フラジャイル</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>賭ケグルイ</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>カッコウの許嫁</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>無職転生 ~異世界行ったら本気だす~</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>貸した魔力はで強制徴収~用済みとパーティー追放された俺は、可愛いサポート妖精と一緒に取り立てた魔力を運用して最強を目指す。~</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>チカーノKEI~米国極悪刑務所を生き抜いた日本人~</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>帝乃三姉妹は案外、チョロい。</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Lv2からチートだった元勇者候補のまったり異世界ライフ</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ダンダダン</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>盤上のオリオン</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>カグラバチ</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>私刑執行人~殺人弁護士とテミスの天秤~</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>弱虫ペダル</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>レッドブルー</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>バブル~チカーノKEI歌舞伎町血闘編~</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>薫る花は凛と咲く</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>シルバーマウンテン</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>青のミブロー新選組編ー</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>魔法少女にあこがれて</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>俺だけ不遇スキルの異世界召喚叛逆記~最弱スキルが全てを飲み込むまで~</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>転生ゴブリンだけど質問ある?</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>焼いてるふたり</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏 ~パーティ事情で付与術士をやっていた剣士、万能へと至る~</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ドッグスレッド</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>うちのちいさな女中さん</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>紛争でしたら八田まで</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>失格紋の最強賢者 ~世界最強の賢者が更に強くなるために転生しました~</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>百瀬アキラの初恋破綻中。</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>帰ってきた天才剣聖~魔力ゼロの落ちこぼれなのに実は最強~</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>新・蒼太の包丁</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>女の園の星</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>最強の剣神、辺境の村娘に生まれ変わる。1</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>帰ってきた天才剣聖~魔力ゼロの落ちこぼれなのに実は最強~</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>便利屋斎藤さん、異世界に来たばかり ~便利屋斎藤さん、異世界に行く 外伝~</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>今日、駅で見た可愛い女の子。</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>静かなるドン ― もうひとつの最終章 ―</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>鬼の花嫁</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>聖者無双</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>勘違いの工房主 英雄パーティの元雑用係が、実は戦闘以外がSSSランクだったというよくある話10</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>救世主《メシア》~異世界を救った元勇者が魔物のあふれる現実世界を無双する~</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>夜鷹ふたたび</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>銭(インチキ)の力で、戦国の世を駆け抜ける。</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>不徳のギルド</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ケンガンオメガ</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>陸奥圓明流異界伝 修羅の紋 ムツさんはチョー強い?!</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>尾守つみきと奇日常。</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>おためしCOMICリュウライブVol.1</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>嫁がされた先は白豚公爵のはずですが?</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>嫁がされた先は白豚公爵のはずですが?</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>嫁がされた先は白豚公爵のはずですが?</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>転生したらラスボス系悪女だった!</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>わたくし、負けませんので。 政略結婚は令嬢のたしなみ</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ラル飯‐ランバ・ラルの背徳ごはん‐</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ラル飯‐ランバ・ラルの背徳ごはん‐</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>追放系の悪役パーティのリーダーに転生したので、ざまぁされる前に自分を追放しました。 ~スキルを奪う『スティール』って悪役過ぎるけど強すぎる~</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>便利屋斎藤さん、異世界に来たばかり ~便利屋斎藤さん、異世界に行く 外伝~</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>便利屋斎藤さん、異世界に来たばかり ~便利屋斎藤さん、異世界に行く 外伝~</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>侯爵令嬢リディアの美しき決断~裏切られたのでこちらから婚約破棄させていただきます~1</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>氷属性男子とクールな同僚女子</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>幼女無双~仲間に裏切られた召喚師、魔族の幼女になってで溺愛スローライフを送る~(ポルカコミックス)5</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>うちの会社の小さい先輩の話</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>十三歳の誕生日、皇后になりました。</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>吸血鬼と愉快な仲間たち</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>転生したら平民でした。~生活水準に耐えられないので貴族を目指します~(コミック)</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>無能なナナ</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>よわよわ先生</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>魔力枯れのダークエルフ</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>雪と墨</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>迷子になっていた幼女を助けたら、お隣に住む美少女留学生が家に遊びに来るようになった件について</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>あなた達それでも先生ですかっ!</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>再召喚された勇者は一般人として生きていく?</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ハズレ属性土魔法のせいで辺境に追放されたので、ガンガン領地開拓します!5</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ゾンビ世界でハーレムをつくろう!</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>スキップとローファー</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>マチネとソワレ</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>殲滅魔導の最強賢者 無才の賢者、魔導を極め最強へ至る</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ダンス・ダンス・ダンスール</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>新テニスの王子様</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>GALAXIAS</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>あの島の海音荘</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>時々ボソッとロシア語でデレる隣のアーリャさん</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>うるわしの宵の月</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>とある魔術の禁書目録</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>人見知り乙女と鬼の婚約者</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>人見知り乙女と鬼の婚約者</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>人見知り乙女と鬼の婚約者</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>私たち離婚しますので</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>私たち離婚しますので</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>私たち離婚しますので</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>白瑞宮のお料理番</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>白瑞宮のお料理番</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>白瑞宮のお料理番</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>転生したらラスボス系悪女だった!</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -56,6 +56,7 @@
     <sheet name="2026-09-16" sheetId="47" state="visible" r:id="rId47"/>
     <sheet name="2026-09-23" sheetId="48" state="visible" r:id="rId48"/>
     <sheet name="2026-09-30" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="2026-10-07" sheetId="50" state="visible" r:id="rId50"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -61194,6 +61195,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>太陽よりも眩しい星</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ドンケツ第2章</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>心を閉ざした公爵閣下と婚約したはずなのに、なぜか大切にされてしまってます!</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>全自動攻撃スキルで俺だけ超速レベルアップ~女神が導く怠惰な転生者のサクッと異世界攻略~</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>フラジャイル</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ちょっと留守にしていたら家が没落していました 転生令嬢は前世知識と聖魔法で大事な家族を救います</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>不機嫌な公爵様はウソ発見器付き令嬢の取説をご所望です</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>転生したら剣でした</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>日に流れて橋に行く</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>黒執事</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ダンダダン</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>お前呼ばわりで婚約破棄?隣国で自由を謳歌するのでどうぞお構いなく!~追放令嬢、実は最強精霊師でした~</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>二度目の人生、(元)罪悪の聖女は前世で少年だった冷徹皇帝に拾われる</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10回婚約破棄された私が冷徹公爵様に溺愛されるなんて罠ですか?</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BUNGO-unreal-</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ジョジョの奇妙な冒険 ザ・ジョジョランズ</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>きみとバラ色の日々</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>きょうはなにしよう?</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>極悪非道な性癖貴族が努力したら誠実ハーレムつくれました</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>住んでる場所が田舎すぎて、ダンジョン探索者が俺一人なんだが?</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>それ、運命のせいではありません1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>魔女の結婚~愛し子の世界征服を手伝いますが、転生のことは秘密です~@comic</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>かがみさまのお屋敷</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>極めて健全な美少女レベルアップ</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>私が聖女?いいえ、悪役令嬢です!~なので、全員破滅は阻止させていただきます~</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>わが家は幽世の貸本屋さん</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>社長が私を抱く理由</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>悪人面したB級冒険者 主人公とその幼馴染たちのパパになる</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>神の庭付き楠木邸</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>超難関ダンジョンで10万年修行した結果、世界最強に ~最弱無能の下剋上~(コミック)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>聖者無双</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>賭ケグルイ</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>隣の元カレくん 単行本版</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>異世界の牧場を相続しました ~スタァストリームファーム~</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ハズレギフト「下限突破」を授かった俺はゼロ以下のステータスで最強を目指す~HP・MP・アイテムが使い放題ってどう考えてもバグすぎません?~</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>因習系邪神様メイリュちゃん</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>自称・お母さんが1体あらわれた!</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>月はタピオカみたいに</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>残光再撮</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ダンジョンマスターは真剣勝負がしたいのに!</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>陛下、今度は私が育てます! 第1話</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>死神少女は陰から推しを眺めたい ─悪役にTS転生したけど、こっそり原作キャラを観察しに行きます!─</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ぜっぴん!子ども食堂</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>追放された付与魔法使いの成り上がり~勇者パーティを陰から支えていたと知らなかったので戻って来い?との美少女たちに囲まれて幸せなので戻りません~(ノヴァコミックス)6</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>雷帝と呼ばれた最強冒険者、魔術学院に入学して一切の遠慮なく無双する(ノヴァコミックス)8</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>転生した空間魔法使いは正体隠して目立ちたい!</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>手に入れた催眠アプリで夢のハーレム生活を送りたい</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>超人X</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり 通常版</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり 通常版</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>失格紋の最強賢者 ~世界最強の賢者が更に強くなるために転生しました~</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>雅血の陰陽師</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ケンガンオメガ</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり 通常版</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>魔入りました!入間くん</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>うるわしの宵の月</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>私が処女で、上司がED。1</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>異世界の牧場を相続しました ~スタァストリームファーム~</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>異世界の牧場を相続しました ~スタァストリームファーム~</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>新人女性漫画家がネットセックスに沼ってVtuberになった話01</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>宵子の肖像</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>年下幼馴染くんに迫られて困ってます!</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Berry’sFantasy地味で無能な次女なので、私のことは忘れてください~私を虐げた家族の皆様、破滅はどうぞご勝手に~</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ほんとは私がいいんでしょ?</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>邪教大戦</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>義弟を虐げて殺される運命の悪役令嬢は何故か彼に溺愛される第1話</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>お飾りの側妃ですね?わかりました。どうぞ私のことは放っといてください!第1話</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>前世で処刑された聖女、今は黒薬師と呼ばれています第1話</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>兄貴の世界は迷走する1</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>きょうはなにしよう?</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>きょうはなにしよう?</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>極悪非道な性癖貴族が努力したら誠実ハーレムつくれました</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>極悪非道な性癖貴族が努力したら誠実ハーレムつくれました</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>住んでる場所が田舎すぎて、ダンジョン探索者が俺一人なんだが?</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>住んでる場所が田舎すぎて、ダンジョン探索者が俺一人なんだが?</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>エンバーミング・マジック</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>極めて健全な美少女レベルアップ</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>極めて健全な美少女レベルアップ</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>魔導具師ダリヤはうつむかない ~王立高等学院編~</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>毒バラの魔女は静かに暮らしたいのに~騎士様からの一途な求婚お断り~ 第1話</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件~外伝~</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>35歳の選択~異世界転生を選んだ場合~(ノヴァコミックス)9</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>異世界チート戦士&amp;魔法使い</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>おっさんのリメイク冒険日記  ~オートキャンプから始まる異世界満喫ライフ~</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>没落貴族の俺がハズレ(?)スキル『超器用貧乏』で大賢者と呼ばれるまで(コミック)</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>鬼の花嫁</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>砂魔法で砂の王国を作ろう ~砂漠に追放されたから頑張って祖国以上の国家を建ててみた~:</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>超人X</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>転生ゴブリンだけど質問ある?</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ハグ キス ハグ</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -57,6 +57,7 @@
     <sheet name="2026-09-23" sheetId="48" state="visible" r:id="rId48"/>
     <sheet name="2026-09-30" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="2026-10-07" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="2026-10-14" sheetId="51" state="visible" r:id="rId51"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -62531,6 +62532,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ワールドトリガー</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BORUTO-ボルト- -TWO BLUE VORTEX-</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>アオアシ ブラザーフット</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>路傍のフジイ</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>魔男のイチ</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>アオのハコ</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>あかね噺</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>逃げ上手の若君</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ふつつかな悪女ではございますが ~雛宮蝶鼠とりかえ伝~:</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ウィッチウォッチ</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>正直不動産</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>傷モノの花嫁</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ドンケツ第2章</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>全自動攻撃スキルで俺だけ超速レベルアップ~女神が導く怠惰な転生者のサクッと異世界攻略~</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>キン肉マン</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>To LOVEる―とらぶる― 短編集 Parade</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sランクパーティから解雇された~『呪いのアイテム』しか作れませんが、その性能はアーティファクト級なり……!~</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1日外出録ハンチョウ</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ゲーム中盤で死ぬ悪役貴族に転生したので、外れスキルを駆使して最強を目指してみた</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ケントゥリア</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ふつうの軽音部</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>こちら葛飾区亀有公園前派出所</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>妹は知っている</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>サンキューピッチ</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>学園ベビーシッターズ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ジョジョの奇妙な冒険 ザ・ジョジョランズ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>不機嫌な公爵様はウソ発見器付き令嬢の取説をご所望です</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>わが家は幽世の貸本屋さん</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>脅され契約妃の白い結婚生活1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>愛し子の結婚~偽装契約なのにエリート騎士様が甘すぎる~1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>二番手の女 歌姫としての誇りを胸に、最後のご奉公をいたします</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>死に戻りの幸薄令嬢、今世では最恐ラスボスお義兄様に溺愛されてます</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>地味な剣聖はそれでも最強です(コミック)12</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>アマチュアビジランテ</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>伍と碁</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>WITCHRIV</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ファントムバスターズ</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>マリッジトキシン</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>悪祓士のキヨシくん</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>心を閉ざした公爵閣下と婚約したはずなのに、なぜか大切にされてしまってます!</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ちいかわ なんか小さくてかわいいやつ</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>貸した魔力はで強制徴収~用済みとパーティー追放された俺は、可愛いサポート妖精と一緒に取り立てた魔力を運用して最強を目指す。~</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>撲殺ピンク~性犯罪者処刑人~</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>超難関ダンジョンで10万年修行した結果、世界最強に ~最弱無能の下剋上~(コミック)</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>だれでも抱けるキミが好き</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>黒執事</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>薬屋のひとりごと</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>スノウボールアース</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>断罪された悪役令嬢は、逆行して完璧な悪女を目指す@COMIC</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>魔入りました!入間くん</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>さむわんへるつ</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>僕とロボコ</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>私が聖女?いいえ、悪役令嬢です!~なので、全員破滅は阻止させていただきます~</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ちょっと留守にしていたら家が没落していました 転生令嬢は前世知識と聖魔法で大事な家族を救います</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>10回婚約破棄された私が冷徹公爵様に溺愛されるなんて罠ですか?</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>そして誰もいなくなった 〔第1話〕</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>クラスの陰キャお嬢様の執事になりました My Pure Lady</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>公爵家の長女でした</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>公爵家の長女でした</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>公爵家の長女でした</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>深夜食堂</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>俺だけ最強超越者~全世界のチート師匠に認められた~</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>転生したら剣でした</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>悪役のご令息のどうにかしたい日常:</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>断罪される公爵令嬢、生まれ変わってラスボスの王妃様の子どもになります</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>フラジャイル</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>才女のお世話7 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>あなた達それでも先生ですかっ!</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ドラフトキング</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>天傍台閣</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>剣に焦ぐ</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>うるわしの宵の月</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>太陽よりも眩しい星</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>追放されたダンジョン配信者、《マッピング》スキルで最強パーティーを目指します1</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>快盗くいしん坊</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>びくびく雅の日常茶飯事</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>お前呼ばわりで婚約破棄?隣国で自由を謳歌するのでどうぞお構いなく!~追放令嬢、実は最強精霊師でした~</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>そして誰もいなくなった 〔第2話〕</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>そして誰もいなくなった 〔第3話〕</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>恋のカスと愛のクズ1</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>令和のおもちゃウーピン1</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>にゃん探偵まる</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>不幸せな公爵令嬢は光の魔女として生きることにしました</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>文鳥Vol.1</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>俺だけ最強超越者~全世界のチート師匠に認められた~</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>修羅幼女の英雄譚~半端者と言われた傭兵、幼女に転生して成り上がる~1</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>冷酷な狼皇帝の契約花嫁~「お前は家族じゃない」と捨てられた令嬢が、獣人国で愛されて幸せになるまで~</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>異世界ハーレムループ~繰り返される1日から脱出する為に抱きまくります~</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>最後の秋、あなたに溺れて 第1話</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>悪役令嬢の躾け方</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>悪役令嬢の躾け方</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -58,6 +58,7 @@
     <sheet name="2026-09-30" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="2026-10-07" sheetId="50" state="visible" r:id="rId50"/>
     <sheet name="2026-10-14" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="2026-10-21" sheetId="52" state="visible" r:id="rId52"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -63868,6 +63869,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>アルスラーン戦記</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>魔入りました!入間くん</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>てんぷる</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>桃源暗鬼</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>異世界賢者の転生無双 ~ゲームの知識で異世界最強~</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ワールドトリガー</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ゆるキャン△</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>信長協奏曲</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>少年院ウシジマくん</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BORUTO-ボルト- -TWO BLUE VORTEX-</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>味方が弱すぎて補助魔法に徹していた宮廷魔法師、追放されて最強を目指す</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1日外出録ハンチョウ</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>アマチュアビジランテ</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>「雑魚には鍛冶がお似合いだwww」と言われた鍛冶レベル9999の俺、追放されたので冒険者に転職する ~最強武器で無双しながらギルドで楽しく暮らします~ コミック版</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>だれでも抱けるキミが好き</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>合コンに行ったら女がいなかった話</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>レベルリセット ~ゴミスキルだと勘違いしたけれど実はとんでもないチートスキルだった~ コミック版</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>やりこみ好きによる領地経営 ~俺だけ見える『開拓度』を上げて最強領地に~ コミック版</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>魔法使いの嫁</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す A Tale of The Great Saint15</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>裏バイト:逃亡禁止</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>アオのハコ</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NINKU―忍空―</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NINKU―忍空―</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NINKU―忍空―</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NINKU―忍空―</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sランクパーティから解雇された~『呪いのアイテム』しか作れませんが、その性能はアーティファクト級なり……!~</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>凶乱令嬢ニア・リストン 病弱令嬢に転生した神殺しの武人の華麗なる無双録</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NINKU―忍空―</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NINKU―忍空―</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>おっさんはうぜぇぇぇんだよ!ってギルドから追放したくせに、後から復帰要請を出されても遅い。最高の仲間と出会った俺はこっちで最強を目指す! コミック版</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>レジスタ!</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>妹は知っている</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>アオアシ ブラザーフット</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>鬼売れアイドルが今日も私を推してくる</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ゲーム中盤で死ぬ悪役貴族に転生したので、外れスキルを駆使して最強を目指してみた</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>世界最強の魔女、始めました ~私だけ『攻略サイト』を見れる世界で自由に生きます~</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>社畜剣聖、配信者になる ~ブラックギルド会社員、うっかり会社用回線でS級モンスターを相手に無双するところを全国配信してしまう~(コミック)</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>魔法使いの嫁</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>じゃあ、あんたが作ってみろよ</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>目指す地位は縁の下。 2(アリアンローズコミックス)</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>悪徳領主の息子に転生!? ~楽しく魔法を学んでいたら、汚名を返上してました~ コミック版</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>錬金術師の辺境再生スローライフ~S級パーティーで孤立した少女をかばったら追放されたので、一緒に幸せに暮らします~2</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>王様ランキング</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で“最強”なのがバレまくる。~老害どもにはいい加減愛想が尽きました~</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>冒険者になりたいと都に出て行った娘がSランクになってた 黒髪の戦乙女10</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>野生のラスボスが現れた! 黒翼の覇王12</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>誰かこの状況を説明してください! ~契約から始まるウェディング~ 12(アリアンローズコミックス)</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>暗殺スキルで異世界最強 ~錬金術と暗殺術を極めた俺は、世界を陰から支配する~</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BUNGO-unreal-</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>塩対応の佐藤さんが俺にだけ甘い@comic</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>魔入りました!入間くん if Episode of 魔フィア</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>あかね噺</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ある日突然、起きられなくなりました ~甲状腺機能低下症との闘い~ (上)</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>すれち恋</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>少年アウルのほんわか異世界ライフ</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>宮廷をクビになった植物魔導師はスローライフを謳歌する~のんびり世界樹を育てたら、最強領地ができました~</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>路傍のフジイ</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件 美食伝~ペコとリムルの料理手帖~</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>税金で買った本</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>傷モノの花嫁</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>無職の英雄 別にスキルなんか要らなかったんだが-才能ゼロの成り上がり-11</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>サイコアイズ</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>貴族転生 ~外伝 14歳ノアの無双旅行~</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>賭ケグルイ</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>魔男のイチ</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>桃源暗鬼</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>桃源暗鬼</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>桃源暗鬼</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>桃源暗鬼</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>桃源暗鬼</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>少年アウルのほんわか異世界ライフ</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>少年アウルのほんわか異世界ライフ</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ダンジョン配信ヒロインは脱衣罠でハーレムフラグが立つらしい</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>きみは四葉のクローバー</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>嫁入りのススメ~大正御曹司の強引な求婚~8</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>異世界から帰還したら地球もかなりファンタジーでした。あと、負けヒロインどもこっち見んな。</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>フラジャイル</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ロメリア戦記~伯爵令嬢、魔王を倒した後も人類やばそうだから軍隊組織する~</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>追放されたチート付与魔術師は気ままなセカンドライフを謳歌する。 ~俺は武器だけじゃなく、あらゆるものに『強化ポイント』を付与できるし、俺の意思でいつでも効果を解除できるけど、残った人たち大丈夫?~</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>かげきしょうじょ!!</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>桃源暗鬼</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>桃源暗鬼</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>モエカレはオレンジ色</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ふしぎ遊戯 白虎仙記</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -59,6 +59,7 @@
     <sheet name="2026-10-07" sheetId="50" state="visible" r:id="rId50"/>
     <sheet name="2026-10-14" sheetId="51" state="visible" r:id="rId51"/>
     <sheet name="2026-10-21" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="2026-10-28" sheetId="53" state="visible" r:id="rId53"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -65205,6 +65206,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア ~クソゲーハンター、神ゲーに挑まんとす~</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>名探偵コナン</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>暁のヨナ</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TSUYOSHI 誰も勝てない、アイツには</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>アルスラーン戦記</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>異世界クラス召喚されたらR1○のスキルを獲得したので、○りたい放題させてもらいます!</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>金田一パパの事件簿</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>廻天のアルバス</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1日外出録ハンチョウ</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>異世界に落とされた…浄化は基本!@COMIC</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>外れスキルだからと追放された《∞チートアビリティ》が強すぎて草も生えない件 ~偶然助けた第三王女にどちゃくそ溺愛されるし、前よりも断然楽しい生活送ってます~ コミック版</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>黒岩メダカに私の可愛いが通じない</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>波うららかに、めおと日和</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>パンプキンナイト</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>転生ゴブリンだけど質問ある?</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ジャンケットバンク</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り 外伝 -人斬りと幼童-</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ワールドトリガー</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NINKU―忍空―</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NINKU―忍空―</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>没落予定の貴族だけど、暇だったから魔法を極めてみた@COMIC</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>魔入りました!入間くん</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NINKU―忍空―</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NINKU―忍空―</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NINKU―忍空―</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NINKU―忍空―</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Shrink~精神科医ヨワイ~</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>モエカレはオレンジ色</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>すだちの魔王城</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>GANTZ:E</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>桃源暗鬼</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ながたんと青と-いちかの料理帖-</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>忍空~SECOND STAGE 干支忍編~</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>パーティ追放から始まる収納無双! ~姪っ子パーティといく最強ハーレム成り上がり~ コミック版</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>俺、勇者じゃないですから。~VR世界の頂点に君臨せし男。転生し、レベル1の無職からリスタートする~</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>だれでも抱けるキミが好き</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>『ショップ』スキルさえあれば、ダンジョン化した世界でも楽勝だ ~迫害された少年の最強ざまぁライフ~</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>合コンに行ったら女がいなかった話</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>釣って食べたいギャル澤さん</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>史上最強の弟子ケンイチ2 ~達人編~</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ダンダダン</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>MAO</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>陽がのぼり菜の花は咲く</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>異世界から帰ってきた勇者は既に擦り切れている。 コミック版</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>攻略難易度ハードモードの地球産ダンジョン ~ボッチが異世界の少女たちと、余裕で攻略するそうです!~ コミック版</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>不滅チーターによる時間回帰無双 ~ダンジョンに籠って1万年。最弱だった俺が失った家族とついでに世界も救います~ コミック版</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>かかと落とし令嬢はチートな踵で無双する ~魔物を即死させて楽しんでいたら、私を追放した実家が崩壊しました~ コミック版</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>裏切られた俺と魔紋スレイブの異世界冒険譚 コミック版</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>勇者パーティーを追い出された死霊魔術師はリッチになって魔王軍で大好きな研究ライフを送る コミック版</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>WORST外伝 ゼットン先生</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>不遇スキルの錬金術師、辺境を開拓する9</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>王太子に婚約破棄されたので、もうバカのふりはやめようと思います</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Sランクパーティから解雇された~『呪いのアイテム』しか作れませんが、その性能はアーティファクト級なり……!~</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ドンケツ第2章</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>裏バイト:逃亡禁止</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>薬屋のひとりごと</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>信長協奏曲</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>乙女ゲームのヒロインで最強サバイバル@COMIC</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>DEAD ROCK</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>魔男のイチ</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BORUTO-ボルト- -TWO BLUE VORTEX-</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>これから幸せになります! 虐げられ令嬢ですが敵対国の公爵様に何故か溺愛されてます</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>店長!エルフちゃんがまたクレーム出してます!@COMIC 第1話</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>私のことは諦めてください!~策士な皇太子と素顔を隠すモブ令嬢の溺愛攻防~1</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>大好きな婚約者様、もうお別れしましょう。1</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>この度、公爵家の令嬢の婚約者となりました。しかし、噂では性格が悪く、十歳も年上です。 コミック版</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>焦がれ王子と純白リリィ 初めてを捧げたらサヨナラの予定だったのに</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>元勇者のおっさん、もう一度世界を救う~魔王討伐後は引退して引きこもり生活をしてたけど世界はそれを許してはくれない件~</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>沙夜ちゃんは元悪の女幹部1</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ゆるキャン△</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>WORST外伝 ドクロ</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>放課後ていぼう日誌</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ダストランド</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
